--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_laag.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_laag.xlsx
@@ -400,22 +400,22 @@
         <v>0.4215077612063589</v>
       </c>
       <c r="C2">
-        <v>0.4831499960849896</v>
+        <v>0.4532370357302815</v>
       </c>
       <c r="D2">
         <v>0.936061968566015</v>
       </c>
       <c r="E2">
-        <v>0.4427977997158401</v>
+        <v>0.442794680589838</v>
       </c>
       <c r="F2">
         <v>0.4238064353770303</v>
       </c>
       <c r="G2">
-        <v>0.5582697136662433</v>
+        <v>0.4931821122603382</v>
       </c>
       <c r="H2">
-        <v>0.4439061019581645</v>
+        <v>0.4439031504368564</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -426,22 +426,22 @@
         <v>0.4480068978269227</v>
       </c>
       <c r="C3">
-        <v>0.5044256551842031</v>
+        <v>0.4823481996652292</v>
       </c>
       <c r="D3">
         <v>0.8665389055668421</v>
       </c>
       <c r="E3">
-        <v>0.4579252394377268</v>
+        <v>0.4579221100507764</v>
       </c>
       <c r="F3">
         <v>0.4491482029126825</v>
       </c>
       <c r="G3">
-        <v>0.5655495099421098</v>
+        <v>0.5153633397146761</v>
       </c>
       <c r="H3">
-        <v>0.4583711003444285</v>
+        <v>0.4583681395719891</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -449,25 +449,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.3758487441489632</v>
+        <v>0.3758487441489631</v>
       </c>
       <c r="C4">
-        <v>0.5238386746799286</v>
+        <v>0.4358399287341901</v>
       </c>
       <c r="D4">
         <v>0.5220626417996851</v>
       </c>
       <c r="E4">
-        <v>0.419720720517589</v>
+        <v>0.4197176574654119</v>
       </c>
       <c r="F4">
         <v>0.3792809828816487</v>
       </c>
       <c r="G4">
-        <v>0.5016439196761076</v>
+        <v>0.4374902955487354</v>
       </c>
       <c r="H4">
-        <v>0.4210993042442046</v>
+        <v>0.4210964053546909</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -478,22 +478,22 @@
         <v>0.4865354429621429</v>
       </c>
       <c r="C5">
-        <v>0.6169197763115375</v>
+        <v>0.5508185575131226</v>
       </c>
       <c r="D5">
         <v>0.3813872425663433</v>
       </c>
       <c r="E5">
-        <v>0.4832906298672929</v>
+        <v>0.4832874750376</v>
       </c>
       <c r="F5">
         <v>0.4857654653692099</v>
       </c>
       <c r="G5">
-        <v>0.5676563923828505</v>
+        <v>0.5298897655057369</v>
       </c>
       <c r="H5">
-        <v>0.4828622496992143</v>
+        <v>0.4828592662848596</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -504,22 +504,22 @@
         <v>0.4768322874951845</v>
       </c>
       <c r="C6">
-        <v>0.6027649171051569</v>
+        <v>0.5359501924988801</v>
       </c>
       <c r="D6">
         <v>0.3079900402865606</v>
       </c>
       <c r="E6">
-        <v>0.4783105745515474</v>
+        <v>0.4783074291455442</v>
       </c>
       <c r="F6">
         <v>0.4764492964914863</v>
       </c>
       <c r="G6">
-        <v>0.5388075863301401</v>
+        <v>0.5057688546224985</v>
       </c>
       <c r="H6">
-        <v>0.4779840328492355</v>
+        <v>0.4779810583617347</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -527,25 +527,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.5011393183364669</v>
+        <v>0.5011393183364667</v>
       </c>
       <c r="C7">
-        <v>0.6641650190029394</v>
+        <v>0.5704041248505743</v>
       </c>
       <c r="D7">
         <v>0.343939944676575</v>
       </c>
       <c r="E7">
-        <v>0.4906483264618737</v>
+        <v>0.4906451742252135</v>
       </c>
       <c r="F7">
         <v>0.5000459747052058</v>
       </c>
       <c r="G7">
-        <v>0.5982250303273913</v>
+        <v>0.5447578938268327</v>
       </c>
       <c r="H7">
-        <v>0.4901282156980983</v>
+        <v>0.490125234680047</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -556,22 +556,22 @@
         <v>0.435592459430847</v>
       </c>
       <c r="C8">
-        <v>0.2655549926585978</v>
+        <v>0.3440101165016323</v>
       </c>
       <c r="D8">
         <v>0.2001018367653793</v>
       </c>
       <c r="E8">
-        <v>0.4243618638141485</v>
+        <v>0.4243587551396946</v>
       </c>
       <c r="F8">
-        <v>0.4343970284190022</v>
+        <v>0.4343970284190021</v>
       </c>
       <c r="G8">
-        <v>0.2714089355384538</v>
+        <v>0.3387555889314413</v>
       </c>
       <c r="H8">
-        <v>0.4238535532033515</v>
+        <v>0.4238506133697998</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -582,22 +582,22 @@
         <v>0.504913894623724</v>
       </c>
       <c r="C9">
-        <v>0.5642381162279333</v>
+        <v>0.5618944707293718</v>
       </c>
       <c r="D9">
         <v>0.5951509372527959</v>
       </c>
       <c r="E9">
-        <v>0.4849542988768999</v>
+        <v>0.4849511372298663</v>
       </c>
       <c r="F9">
         <v>0.503969351370773</v>
       </c>
       <c r="G9">
-        <v>0.5289994715570385</v>
+        <v>0.5507354905628262</v>
       </c>
       <c r="H9">
-        <v>0.4846115032126928</v>
+        <v>0.4846085133053303</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -608,22 +608,22 @@
         <v>0.5196008561227122</v>
       </c>
       <c r="C10">
-        <v>0.6356681456836951</v>
+        <v>0.5751234693798278</v>
       </c>
       <c r="D10">
         <v>0.4861278178718842</v>
       </c>
       <c r="E10">
-        <v>0.4948320011300388</v>
+        <v>0.4948288880490032</v>
       </c>
       <c r="F10">
         <v>0.5183759225260688</v>
       </c>
       <c r="G10">
-        <v>0.6289567929654097</v>
+        <v>0.5757433387719072</v>
       </c>
       <c r="H10">
-        <v>0.4945581757406573</v>
+        <v>0.4945552277675513</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -631,25 +631,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.514738428575523</v>
+        <v>0.5147384285755229</v>
       </c>
       <c r="C11">
-        <v>0.6385936188818586</v>
+        <v>0.5761168760917758</v>
       </c>
       <c r="D11">
         <v>0.42736632153673</v>
       </c>
       <c r="E11">
-        <v>0.4944173734453672</v>
+        <v>0.49457034641241</v>
       </c>
       <c r="F11">
         <v>0.5135506171930706</v>
       </c>
       <c r="G11">
-        <v>0.6226942439590685</v>
+        <v>0.5695263211412293</v>
       </c>
       <c r="H11">
-        <v>0.4940951649490354</v>
+        <v>0.4942478810724729</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -660,22 +660,22 @@
         <v>0.4804581224628028</v>
       </c>
       <c r="C12">
-        <v>0.6520636925742531</v>
+        <v>0.6352131230705311</v>
       </c>
       <c r="D12">
         <v>0.1055451499878177</v>
       </c>
       <c r="E12">
-        <v>0.4849535997546612</v>
+        <v>0.4850647510340158</v>
       </c>
       <c r="F12">
         <v>0.4800854062337293</v>
       </c>
       <c r="G12">
-        <v>0.5745126601619753</v>
+        <v>0.5945354592179901</v>
       </c>
       <c r="H12">
-        <v>0.4846629971429635</v>
+        <v>0.4847648522690444</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -686,22 +686,22 @@
         <v>0.517283874555091</v>
       </c>
       <c r="C13">
-        <v>0.634076234566488</v>
+        <v>0.5719969355166875</v>
       </c>
       <c r="D13">
         <v>0.3713265864090526</v>
       </c>
       <c r="E13">
-        <v>0.4938201023773014</v>
+        <v>0.4938169932699378</v>
       </c>
       <c r="F13">
         <v>0.5160629930030343</v>
       </c>
       <c r="G13">
-        <v>0.6127564029467489</v>
+        <v>0.5618534312278398</v>
       </c>
       <c r="H13">
-        <v>0.4935167979719632</v>
+        <v>0.4935138543068217</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_laag.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_laag.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
@@ -28,7 +28,10 @@
     <t>OV</t>
   </si>
   <si>
-    <t>Auto-FietsOV_Fiets</t>
+    <t>Auto-Fiets</t>
+  </si>
+  <si>
+    <t>OV_Fiets</t>
   </si>
   <si>
     <t>Auto_OV</t>
@@ -391,6 +394,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2">

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_laag.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_laag.xlsx
@@ -403,25 +403,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.4215077612063589</v>
+        <v>1.424292393106278</v>
       </c>
       <c r="C2">
-        <v>0.4532370357302815</v>
+        <v>1.531506941692202</v>
       </c>
       <c r="D2">
-        <v>0.936061968566015</v>
+        <v>3.162992627914984</v>
       </c>
       <c r="E2">
-        <v>0.442794680589838</v>
+        <v>1.496221785969136</v>
       </c>
       <c r="F2">
-        <v>0.4238064353770303</v>
+        <v>1.432059709480588</v>
       </c>
       <c r="G2">
-        <v>0.4931821122603382</v>
+        <v>1.66648302963179</v>
       </c>
       <c r="H2">
-        <v>0.4439031504368564</v>
+        <v>1.499967352045018</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -429,25 +429,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.4480068978269227</v>
+        <v>0.8492068557177033</v>
       </c>
       <c r="C3">
-        <v>0.4823481996652292</v>
+        <v>0.9143015430915289</v>
       </c>
       <c r="D3">
-        <v>0.8665389055668421</v>
+        <v>1.64254341377968</v>
       </c>
       <c r="E3">
-        <v>0.4579221100507764</v>
+        <v>0.8680013569569356</v>
       </c>
       <c r="F3">
-        <v>0.4491482029126825</v>
+        <v>0.8513702244247343</v>
       </c>
       <c r="G3">
-        <v>0.5153633397146761</v>
+        <v>0.9768824618418059</v>
       </c>
       <c r="H3">
-        <v>0.4583681395719891</v>
+        <v>0.8688468156521109</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -455,25 +455,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.3758487441489631</v>
+        <v>0.916807182218804</v>
       </c>
       <c r="C4">
-        <v>0.4358399287341901</v>
+        <v>1.063143573529856</v>
       </c>
       <c r="D4">
-        <v>0.5220626417996851</v>
+        <v>1.2734664862426</v>
       </c>
       <c r="E4">
-        <v>0.4197176574654119</v>
+        <v>1.023816545508612</v>
       </c>
       <c r="F4">
-        <v>0.3792809828816487</v>
+        <v>0.9251794361379728</v>
       </c>
       <c r="G4">
-        <v>0.4374902955487354</v>
+        <v>1.067169310405196</v>
       </c>
       <c r="H4">
-        <v>0.4210964053546909</v>
+        <v>1.027179722816074</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -481,25 +481,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.4865354429621429</v>
+        <v>0.1212572853202864</v>
       </c>
       <c r="C5">
-        <v>0.5508185575131226</v>
+        <v>0.1372783092254067</v>
       </c>
       <c r="D5">
-        <v>0.3813872425663433</v>
+        <v>0.09505161927737039</v>
       </c>
       <c r="E5">
-        <v>0.4832874750376</v>
+        <v>0.120447807246213</v>
       </c>
       <c r="F5">
-        <v>0.4857654653692099</v>
+        <v>0.1210653868799424</v>
       </c>
       <c r="G5">
-        <v>0.5298897655057369</v>
+        <v>0.1320623099789839</v>
       </c>
       <c r="H5">
-        <v>0.4828592662848596</v>
+        <v>0.1203410864889511</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -507,25 +507,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.4768322874951845</v>
+        <v>0.5249365371640472</v>
       </c>
       <c r="C6">
-        <v>0.5359501924988801</v>
+        <v>0.5900184310518355</v>
       </c>
       <c r="D6">
-        <v>0.3079900402865606</v>
+        <v>0.3390609853169292</v>
       </c>
       <c r="E6">
-        <v>0.4783074291455442</v>
+        <v>0.5265604954614896</v>
       </c>
       <c r="F6">
-        <v>0.4764492964914863</v>
+        <v>0.5245149088965858</v>
       </c>
       <c r="G6">
-        <v>0.5057688546224985</v>
+        <v>0.5567923106583715</v>
       </c>
       <c r="H6">
-        <v>0.4779810583617347</v>
+        <v>0.5262011994289484</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -533,25 +533,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.5011393183364667</v>
+        <v>0.9521647048392868</v>
       </c>
       <c r="C7">
-        <v>0.5704041248505743</v>
+        <v>1.083767837216091</v>
       </c>
       <c r="D7">
-        <v>0.343939944676575</v>
+        <v>0.6534858948854926</v>
       </c>
       <c r="E7">
-        <v>0.4906451742252135</v>
+        <v>0.9322258310279056</v>
       </c>
       <c r="F7">
-        <v>0.5000459747052058</v>
+        <v>0.950087351939891</v>
       </c>
       <c r="G7">
-        <v>0.5447578938268327</v>
+        <v>1.035039998270982</v>
       </c>
       <c r="H7">
-        <v>0.490125234680047</v>
+        <v>0.9312379458920891</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -559,25 +559,25 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.435592459430847</v>
+        <v>0.1088650452813808</v>
       </c>
       <c r="C8">
-        <v>0.3440101165016323</v>
+        <v>0.0859764123537332</v>
       </c>
       <c r="D8">
-        <v>0.2001018367653793</v>
+        <v>0.05001026773698974</v>
       </c>
       <c r="E8">
-        <v>0.4243587551396946</v>
+        <v>0.1060574720558666</v>
       </c>
       <c r="F8">
-        <v>0.4343970284190021</v>
+        <v>0.1085662782838867</v>
       </c>
       <c r="G8">
-        <v>0.3387555889314413</v>
+        <v>0.08466317937764234</v>
       </c>
       <c r="H8">
-        <v>0.4238506133697998</v>
+        <v>0.1059304751908124</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -585,25 +585,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.504913894623724</v>
+        <v>0.9376146280210786</v>
       </c>
       <c r="C9">
-        <v>0.5618944707293718</v>
+        <v>1.043426375803417</v>
       </c>
       <c r="D9">
-        <v>0.5951509372527959</v>
+        <v>1.105182944241474</v>
       </c>
       <c r="E9">
-        <v>0.4849511372298663</v>
+        <v>0.9005442016624109</v>
       </c>
       <c r="F9">
-        <v>0.503969351370773</v>
+        <v>0.9358606307946299</v>
       </c>
       <c r="G9">
-        <v>0.5507354905628262</v>
+        <v>1.022704381124013</v>
       </c>
       <c r="H9">
-        <v>0.4846085133053303</v>
+        <v>0.8999079561421832</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -611,25 +611,25 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.5196008561227122</v>
+        <v>0.1306510823198727</v>
       </c>
       <c r="C10">
-        <v>0.5751234693798278</v>
+        <v>0.1446119706244076</v>
       </c>
       <c r="D10">
-        <v>0.4861278178718842</v>
+        <v>0.1222344513146067</v>
       </c>
       <c r="E10">
-        <v>0.4948288880490032</v>
+        <v>0.1244222926597205</v>
       </c>
       <c r="F10">
-        <v>0.5183759225260688</v>
+        <v>0.1303430787854566</v>
       </c>
       <c r="G10">
-        <v>0.5757433387719072</v>
+        <v>0.1447678337374449</v>
       </c>
       <c r="H10">
-        <v>0.4945552277675513</v>
+        <v>0.1243534821265231</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -637,25 +637,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.5147384285755229</v>
+        <v>0.1328357235033607</v>
       </c>
       <c r="C11">
-        <v>0.5761168760917758</v>
+        <v>0.1486753228623937</v>
       </c>
       <c r="D11">
-        <v>0.42736632153673</v>
+        <v>0.1102880829772206</v>
       </c>
       <c r="E11">
-        <v>0.49457034641241</v>
+        <v>0.1276310571386865</v>
       </c>
       <c r="F11">
-        <v>0.5135506171930706</v>
+        <v>0.1325291915336956</v>
       </c>
       <c r="G11">
-        <v>0.5695263211412293</v>
+        <v>0.1469745344880592</v>
       </c>
       <c r="H11">
-        <v>0.4942478810724729</v>
+        <v>0.1275478402767672</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -663,25 +663,25 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.4804581224628028</v>
+        <v>0.4468942354954813</v>
       </c>
       <c r="C12">
-        <v>0.6352131230705311</v>
+        <v>0.5908383472761032</v>
       </c>
       <c r="D12">
-        <v>0.1055451499878177</v>
+        <v>0.09817196735541382</v>
       </c>
       <c r="E12">
-        <v>0.4850647510340158</v>
+        <v>0.4511790537913842</v>
       </c>
       <c r="F12">
-        <v>0.4800854062337293</v>
+        <v>0.4465475565104434</v>
       </c>
       <c r="G12">
-        <v>0.5945354592179901</v>
+        <v>0.5530023473434954</v>
       </c>
       <c r="H12">
-        <v>0.4847648522690444</v>
+        <v>0.4509001053814565</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -689,25 +689,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.517283874555091</v>
+        <v>0.1299841530933305</v>
       </c>
       <c r="C13">
-        <v>0.5719969355166875</v>
+        <v>0.1437325632836805</v>
       </c>
       <c r="D13">
-        <v>0.3713265864090526</v>
+        <v>0.09330770632842858</v>
       </c>
       <c r="E13">
-        <v>0.4938169932699378</v>
+        <v>0.1240873470268048</v>
       </c>
       <c r="F13">
-        <v>0.5160629930030343</v>
+        <v>0.1296773674725573</v>
       </c>
       <c r="G13">
-        <v>0.5618534312278398</v>
+        <v>0.1411836827187905</v>
       </c>
       <c r="H13">
-        <v>0.4935138543068217</v>
+        <v>0.1240111736463295</v>
       </c>
     </row>
   </sheetData>
